--- a/ROSA_vitaSPEC/Results/xgboost/moyennes/Results/HR/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
+++ b/ROSA_vitaSPEC/Results/xgboost/moyennes/Results/HR/C18.1n9/RANDOMSEARCH_DETAILS_C18.1n9.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2609,29 +2609,29 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9905</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0.1516</v>
+        <v>0.6163</v>
       </c>
       <c r="G69" t="n">
-        <v>0.7427</v>
+        <v>0.0054</v>
       </c>
       <c r="H69" t="n">
-        <v>2.6651</v>
+        <v>1.7923</v>
       </c>
     </row>
     <row r="70">
@@ -2641,29 +2641,29 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(1,3,21))</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0.1442</v>
+        <v>0.6409</v>
       </c>
       <c r="G70" t="n">
-        <v>0.7647</v>
+        <v>0.0067</v>
       </c>
       <c r="H70" t="n">
-        <v>2.6768</v>
+        <v>1.734</v>
       </c>
     </row>
     <row r="71">
@@ -2673,29 +2673,29 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1341</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0054</v>
       </c>
       <c r="H71" t="n">
-        <v>2.6925</v>
+        <v>1.4276</v>
       </c>
     </row>
     <row r="72">
@@ -2705,29 +2705,29 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1100,600,1)), list('snv',''), list('sder',c(2,3,21))</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E72" t="n">
         <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0.139</v>
+        <v>0.7419</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0208</v>
+        <v>0.0003</v>
       </c>
       <c r="H72" t="n">
-        <v>2.6849</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="73">
@@ -2737,29 +2737,29 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,11)), list('snv','')</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 300, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0.9905</v>
       </c>
       <c r="F73" t="n">
-        <v>0.369</v>
+        <v>0.1516</v>
       </c>
       <c r="G73" t="n">
-        <v>0.0016</v>
+        <v>0.7427</v>
       </c>
       <c r="H73" t="n">
-        <v>2.2986</v>
+        <v>2.6651</v>
       </c>
     </row>
     <row r="74">
@@ -2769,29 +2769,29 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,2,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F74" t="n">
-        <v>0.5195</v>
+        <v>0.1442</v>
       </c>
       <c r="G74" t="n">
-        <v>0.0005</v>
+        <v>0.7647</v>
       </c>
       <c r="H74" t="n">
-        <v>2.0058</v>
+        <v>2.6768</v>
       </c>
     </row>
     <row r="75">
@@ -2801,29 +2801,29 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9794</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.0335</v>
+        <v>0.1341</v>
       </c>
       <c r="G75" t="n">
-        <v>1.668</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H75" t="n">
-        <v>2.9416</v>
+        <v>2.6925</v>
       </c>
     </row>
     <row r="76">
@@ -2833,29 +2833,29 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,21)), list('snv','')</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9794</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.0335</v>
+        <v>0.139</v>
       </c>
       <c r="G76" t="n">
-        <v>1.668</v>
+        <v>0.0208</v>
       </c>
       <c r="H76" t="n">
-        <v>2.9416</v>
+        <v>2.6849</v>
       </c>
     </row>
     <row r="77">
@@ -2865,29 +2865,29 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('snv','')</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 300, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.9865</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0.155</v>
+        <v>0.369</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8315</v>
+        <v>0.0016</v>
       </c>
       <c r="H77" t="n">
-        <v>2.6598</v>
+        <v>2.2986</v>
       </c>
     </row>
     <row r="78">
@@ -2897,29 +2897,29 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,21)), list('snv','')</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>0.1659</v>
+        <v>0.5195</v>
       </c>
       <c r="G78" t="n">
-        <v>0.0004</v>
+        <v>0.0005</v>
       </c>
       <c r="H78" t="n">
-        <v>2.6426</v>
+        <v>2.0058</v>
       </c>
     </row>
     <row r="79">
@@ -2929,29 +2929,29 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>0.9794</v>
       </c>
       <c r="F79" t="n">
-        <v>0.1646</v>
+        <v>-0.0335</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0004</v>
+        <v>1.668</v>
       </c>
       <c r="H79" t="n">
-        <v>2.6447</v>
+        <v>2.9416</v>
       </c>
     </row>
     <row r="80">
@@ -2961,29 +2961,29 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3')</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.9854000000000001</v>
+        <v>0.9794</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1663</v>
+        <v>-0.0335</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8429</v>
+        <v>1.668</v>
       </c>
       <c r="H80" t="n">
-        <v>2.6419</v>
+        <v>2.9416</v>
       </c>
     </row>
     <row r="81">
@@ -2993,29 +2993,29 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>0.9865</v>
       </c>
       <c r="F81" t="n">
-        <v>0.585</v>
+        <v>0.155</v>
       </c>
       <c r="G81" t="n">
-        <v>0.0003</v>
+        <v>0.8315</v>
       </c>
       <c r="H81" t="n">
-        <v>1.8641</v>
+        <v>2.6598</v>
       </c>
     </row>
     <row r="82">
@@ -3025,29 +3025,29 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>0.5623</v>
+        <v>0.1659</v>
       </c>
       <c r="G82" t="n">
-        <v>0.0071</v>
+        <v>0.0004</v>
       </c>
       <c r="H82" t="n">
-        <v>1.9143</v>
+        <v>2.6426</v>
       </c>
     </row>
     <row r="83">
@@ -3057,29 +3057,29 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9806</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.0372</v>
+        <v>0.1646</v>
       </c>
       <c r="G83" t="n">
-        <v>1.6704</v>
+        <v>0.0004</v>
       </c>
       <c r="H83" t="n">
-        <v>2.9468</v>
+        <v>2.6447</v>
       </c>
     </row>
     <row r="84">
@@ -3089,29 +3089,29 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9805</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.0273</v>
+        <v>0.1663</v>
       </c>
       <c r="G84" t="n">
-        <v>1.6701</v>
+        <v>0.8429</v>
       </c>
       <c r="H84" t="n">
-        <v>2.9328</v>
+        <v>2.6419</v>
       </c>
     </row>
     <row r="85">
@@ -3121,29 +3121,29 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9807</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.0372</v>
+        <v>0.585</v>
       </c>
       <c r="G85" t="n">
-        <v>1.6708</v>
+        <v>0.0003</v>
       </c>
       <c r="H85" t="n">
-        <v>2.9469</v>
+        <v>1.8641</v>
       </c>
     </row>
     <row r="86">
@@ -3153,29 +3153,29 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9995000000000001</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2795</v>
+        <v>0.5623</v>
       </c>
       <c r="G86" t="n">
-        <v>0.1166</v>
+        <v>0.0071</v>
       </c>
       <c r="H86" t="n">
-        <v>2.4561</v>
+        <v>1.9143</v>
       </c>
     </row>
     <row r="87">
@@ -3185,29 +3185,29 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9806</v>
       </c>
       <c r="F87" t="n">
-        <v>0.2429</v>
+        <v>-0.0372</v>
       </c>
       <c r="G87" t="n">
-        <v>0.1248</v>
+        <v>1.6704</v>
       </c>
       <c r="H87" t="n">
-        <v>2.5178</v>
+        <v>2.9468</v>
       </c>
     </row>
     <row r="88">
@@ -3217,29 +3217,29 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 1.0}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0.9805</v>
       </c>
       <c r="F88" t="n">
-        <v>0.272</v>
+        <v>-0.0273</v>
       </c>
       <c r="G88" t="n">
-        <v>0.0094</v>
+        <v>1.6701</v>
       </c>
       <c r="H88" t="n">
-        <v>2.4689</v>
+        <v>2.9328</v>
       </c>
     </row>
     <row r="89">
@@ -3249,29 +3249,29 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0.9807</v>
       </c>
       <c r="F89" t="n">
-        <v>0.2474</v>
+        <v>-0.0372</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0004</v>
+        <v>1.6708</v>
       </c>
       <c r="H89" t="n">
-        <v>2.5102</v>
+        <v>2.9469</v>
       </c>
     </row>
     <row r="90">
@@ -3281,29 +3281,29 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 9))</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4894</v>
+        <v>0.2795</v>
       </c>
       <c r="G90" t="n">
-        <v>0.0034</v>
+        <v>0.1166</v>
       </c>
       <c r="H90" t="n">
-        <v>2.0675</v>
+        <v>2.4561</v>
       </c>
     </row>
     <row r="91">
@@ -3313,29 +3313,29 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 11))</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F91" t="n">
-        <v>0.4772</v>
+        <v>0.2429</v>
       </c>
       <c r="G91" t="n">
-        <v>0.0032</v>
+        <v>0.1248</v>
       </c>
       <c r="H91" t="n">
-        <v>2.0921</v>
+        <v>2.5178</v>
       </c>
     </row>
     <row r="92">
@@ -3345,11 +3345,11 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3377,29 +3377,29 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1, 3, 21))</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E93" t="n">
         <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4772</v>
+        <v>0.2474</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0032</v>
+        <v>0.0004</v>
       </c>
       <c r="H93" t="n">
-        <v>2.0921</v>
+        <v>2.5102</v>
       </c>
     </row>
     <row r="94">
@@ -3409,29 +3409,29 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 15))</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.979</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.0008</v>
+        <v>0.4894</v>
       </c>
       <c r="G94" t="n">
-        <v>1.634</v>
+        <v>0.0034</v>
       </c>
       <c r="H94" t="n">
-        <v>2.8946</v>
+        <v>2.0675</v>
       </c>
     </row>
     <row r="95">
@@ -3441,29 +3441,29 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8846000000000001</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0.046</v>
+        <v>0.4772</v>
       </c>
       <c r="G95" t="n">
-        <v>1.7518</v>
+        <v>0.0032</v>
       </c>
       <c r="H95" t="n">
-        <v>2.8262</v>
+        <v>2.0921</v>
       </c>
     </row>
     <row r="96">
@@ -3473,29 +3473,29 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 1.0}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9564</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>0.007</v>
+        <v>0.272</v>
       </c>
       <c r="G96" t="n">
-        <v>1.733</v>
+        <v>0.0094</v>
       </c>
       <c r="H96" t="n">
-        <v>2.8833</v>
+        <v>2.4689</v>
       </c>
     </row>
     <row r="97">
@@ -3505,29 +3505,29 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9775</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>-0.0017</v>
+        <v>0.4772</v>
       </c>
       <c r="G97" t="n">
-        <v>1.6427</v>
+        <v>0.0032</v>
       </c>
       <c r="H97" t="n">
-        <v>2.896</v>
+        <v>2.0921</v>
       </c>
     </row>
     <row r="98">
@@ -3537,29 +3537,29 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9996</v>
+        <v>0.979</v>
       </c>
       <c r="F98" t="n">
-        <v>0.2173</v>
+        <v>-0.0008</v>
       </c>
       <c r="G98" t="n">
-        <v>0.119</v>
+        <v>1.634</v>
       </c>
       <c r="H98" t="n">
-        <v>2.5599</v>
+        <v>2.8946</v>
       </c>
     </row>
     <row r="99">
@@ -3569,29 +3569,29 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1821</v>
+        <v>0.046</v>
       </c>
       <c r="G99" t="n">
-        <v>0.011</v>
+        <v>1.7518</v>
       </c>
       <c r="H99" t="n">
-        <v>2.6168</v>
+        <v>2.8262</v>
       </c>
     </row>
     <row r="100">
@@ -3601,29 +3601,29 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 2, 15))</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9911</v>
+        <v>0.9564</v>
       </c>
       <c r="F100" t="n">
-        <v>0.1642</v>
+        <v>0.007</v>
       </c>
       <c r="G100" t="n">
-        <v>0.7533</v>
+        <v>1.733</v>
       </c>
       <c r="H100" t="n">
-        <v>2.6454</v>
+        <v>2.8833</v>
       </c>
     </row>
     <row r="101">
@@ -3633,29 +3633,29 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.994</v>
+        <v>0.9775</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1329</v>
+        <v>-0.0017</v>
       </c>
       <c r="G101" t="n">
-        <v>0.6283</v>
+        <v>1.6427</v>
       </c>
       <c r="H101" t="n">
-        <v>2.6944</v>
+        <v>2.896</v>
       </c>
     </row>
     <row r="102">
@@ -3665,29 +3665,29 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 5))</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9937</v>
+        <v>0.9996</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1057</v>
+        <v>0.2173</v>
       </c>
       <c r="G102" t="n">
-        <v>0.6444</v>
+        <v>0.119</v>
       </c>
       <c r="H102" t="n">
-        <v>2.7363</v>
+        <v>2.5599</v>
       </c>
     </row>
     <row r="103">
@@ -3697,29 +3697,29 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 11))</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9688</v>
+        <v>1</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0983</v>
+        <v>0.1821</v>
       </c>
       <c r="G103" t="n">
-        <v>1.2946</v>
+        <v>0.011</v>
       </c>
       <c r="H103" t="n">
-        <v>2.7477</v>
+        <v>2.6168</v>
       </c>
     </row>
     <row r="104">
@@ -3729,29 +3729,29 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 15))</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9986</v>
+        <v>0.9911</v>
       </c>
       <c r="F104" t="n">
-        <v>0.2009</v>
+        <v>0.1642</v>
       </c>
       <c r="G104" t="n">
-        <v>0.2602</v>
+        <v>0.7533</v>
       </c>
       <c r="H104" t="n">
-        <v>2.5865</v>
+        <v>2.6454</v>
       </c>
     </row>
     <row r="105">
@@ -3761,29 +3761,29 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 21))</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9919</v>
+        <v>0.994</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1556</v>
+        <v>0.1329</v>
       </c>
       <c r="G105" t="n">
-        <v>0.7138</v>
+        <v>0.6283</v>
       </c>
       <c r="H105" t="n">
-        <v>2.6588</v>
+        <v>2.6944</v>
       </c>
     </row>
     <row r="106">
@@ -3793,29 +3793,29 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 2, 31))</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 500, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9993</v>
+        <v>0.9937</v>
       </c>
       <c r="F106" t="n">
-        <v>0.17</v>
+        <v>0.1057</v>
       </c>
       <c r="G106" t="n">
-        <v>0.1825</v>
+        <v>0.6444</v>
       </c>
       <c r="H106" t="n">
-        <v>2.6361</v>
+        <v>2.7363</v>
       </c>
     </row>
     <row r="107">
@@ -3825,29 +3825,29 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 5))</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>0.9688</v>
       </c>
       <c r="F107" t="n">
-        <v>0.1716</v>
+        <v>0.0983</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0003</v>
+        <v>1.2946</v>
       </c>
       <c r="H107" t="n">
-        <v>2.6336</v>
+        <v>2.7477</v>
       </c>
     </row>
     <row r="108">
@@ -3857,29 +3857,29 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 11))</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 500, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9996</v>
+        <v>0.9986</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3883</v>
+        <v>0.2009</v>
       </c>
       <c r="G108" t="n">
-        <v>0.1287</v>
+        <v>0.2602</v>
       </c>
       <c r="H108" t="n">
-        <v>2.263</v>
+        <v>2.5865</v>
       </c>
     </row>
     <row r="109">
@@ -3889,29 +3889,29 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 15))</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1</v>
+        <v>0.9919</v>
       </c>
       <c r="F109" t="n">
-        <v>0.4091</v>
+        <v>0.1556</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0032</v>
+        <v>0.7138</v>
       </c>
       <c r="H109" t="n">
-        <v>2.2242</v>
+        <v>2.6588</v>
       </c>
     </row>
     <row r="110">
@@ -3921,29 +3921,29 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 21))</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 500, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>0.9993</v>
       </c>
       <c r="F110" t="n">
-        <v>0.4657</v>
+        <v>0.17</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0042</v>
+        <v>0.1825</v>
       </c>
       <c r="H110" t="n">
-        <v>2.115</v>
+        <v>2.6361</v>
       </c>
     </row>
     <row r="111">
@@ -3953,29 +3953,29 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1, 3, 31))</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E111" t="n">
         <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>0.4567</v>
+        <v>0.1716</v>
       </c>
       <c r="G111" t="n">
         <v>0.0003</v>
       </c>
       <c r="H111" t="n">
-        <v>2.1328</v>
+        <v>2.6336</v>
       </c>
     </row>
     <row r="112">
@@ -3985,11 +3985,11 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 11))</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4001,13 +4001,13 @@
         <v>0.9996</v>
       </c>
       <c r="F112" t="n">
-        <v>0.3982</v>
+        <v>0.3883</v>
       </c>
       <c r="G112" t="n">
-        <v>0.128</v>
+        <v>0.1287</v>
       </c>
       <c r="H112" t="n">
-        <v>2.2446</v>
+        <v>2.263</v>
       </c>
     </row>
     <row r="113">
@@ -4017,29 +4017,29 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 15))</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E113" t="n">
         <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>0.4213</v>
+        <v>0.4091</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0003</v>
+        <v>0.0032</v>
       </c>
       <c r="H113" t="n">
-        <v>2.2013</v>
+        <v>2.2242</v>
       </c>
     </row>
     <row r="114">
@@ -4049,11 +4049,11 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 21))</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4065,13 +4065,13 @@
         <v>1</v>
       </c>
       <c r="F114" t="n">
-        <v>0.4696</v>
+        <v>0.4657</v>
       </c>
       <c r="G114" t="n">
-        <v>0.003</v>
+        <v>0.0042</v>
       </c>
       <c r="H114" t="n">
-        <v>2.1073</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="115">
@@ -4081,29 +4081,29 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 2, 31))</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E115" t="n">
         <v>1</v>
       </c>
       <c r="F115" t="n">
-        <v>0.4754</v>
+        <v>0.4567</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0055</v>
+        <v>0.0003</v>
       </c>
       <c r="H115" t="n">
-        <v>2.0957</v>
+        <v>2.1328</v>
       </c>
     </row>
     <row r="116">
@@ -4113,29 +4113,29 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 11))</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 500, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4649</v>
+        <v>0.3982</v>
       </c>
       <c r="G116" t="n">
-        <v>0.0098</v>
+        <v>0.128</v>
       </c>
       <c r="H116" t="n">
-        <v>2.1166</v>
+        <v>2.2446</v>
       </c>
     </row>
     <row r="117">
@@ -4145,29 +4145,29 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 15))</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.9987</v>
+        <v>1</v>
       </c>
       <c r="F117" t="n">
-        <v>0.4721</v>
+        <v>0.4213</v>
       </c>
       <c r="G117" t="n">
-        <v>0.1681</v>
+        <v>0.0003</v>
       </c>
       <c r="H117" t="n">
-        <v>2.1024</v>
+        <v>2.2013</v>
       </c>
     </row>
     <row r="118">
@@ -4177,29 +4177,29 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 21))</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9919</v>
+        <v>1</v>
       </c>
       <c r="F118" t="n">
-        <v>0.1556</v>
+        <v>0.4696</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7138</v>
+        <v>0.003</v>
       </c>
       <c r="H118" t="n">
-        <v>2.6588</v>
+        <v>2.1073</v>
       </c>
     </row>
     <row r="119">
@@ -4209,29 +4209,29 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2, 3, 31))</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E119" t="n">
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>0.4213</v>
+        <v>0.4754</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0003</v>
+        <v>0.0055</v>
       </c>
       <c r="H119" t="n">
-        <v>2.2013</v>
+        <v>2.0957</v>
       </c>
     </row>
     <row r="120">
@@ -4241,29 +4241,29 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9776</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.0059</v>
+        <v>0.4649</v>
       </c>
       <c r="G120" t="n">
-        <v>1.664</v>
+        <v>0.0098</v>
       </c>
       <c r="H120" t="n">
-        <v>2.9021</v>
+        <v>2.1166</v>
       </c>
     </row>
     <row r="121">
@@ -4273,29 +4273,29 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
+          <t>list('adj',''), list('red',c(950,750,1)), list('msc',''), list('sder',c(1,3,21))</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9776</v>
+        <v>0.9987</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.0059</v>
+        <v>0.4721</v>
       </c>
       <c r="G121" t="n">
-        <v>1.664</v>
+        <v>0.1681</v>
       </c>
       <c r="H121" t="n">
-        <v>2.9021</v>
+        <v>2.1024</v>
       </c>
     </row>
     <row r="122">
@@ -4305,29 +4305,29 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(1,3,15)), list('msc','')</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1</v>
+        <v>0.9919</v>
       </c>
       <c r="F122" t="n">
-        <v>0.082</v>
+        <v>0.1556</v>
       </c>
       <c r="G122" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.7138</v>
       </c>
       <c r="H122" t="n">
-        <v>2.7723</v>
+        <v>2.6588</v>
       </c>
     </row>
     <row r="123">
@@ -4337,29 +4337,29 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,3,15)), list('msc','')</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E123" t="n">
         <v>1</v>
       </c>
       <c r="F123" t="n">
-        <v>0.4042</v>
+        <v>0.4213</v>
       </c>
       <c r="G123" t="n">
-        <v>0.0034</v>
+        <v>0.0003</v>
       </c>
       <c r="H123" t="n">
-        <v>2.2334</v>
+        <v>2.2013</v>
       </c>
     </row>
     <row r="124">
@@ -4369,29 +4369,29 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9997</v>
+        <v>0.9776</v>
       </c>
       <c r="F124" t="n">
-        <v>0.4525</v>
+        <v>-0.0059</v>
       </c>
       <c r="G124" t="n">
-        <v>0.0849</v>
+        <v>1.664</v>
       </c>
       <c r="H124" t="n">
-        <v>2.1411</v>
+        <v>2.9021</v>
       </c>
     </row>
     <row r="125">
@@ -4401,11 +4401,11 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3')</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4414,16 +4414,16 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9794</v>
+        <v>0.9776</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.0024</v>
+        <v>-0.0059</v>
       </c>
       <c r="G125" t="n">
-        <v>1.6304</v>
+        <v>1.664</v>
       </c>
       <c r="H125" t="n">
-        <v>2.8969</v>
+        <v>2.9021</v>
       </c>
     </row>
     <row r="126">
@@ -4433,29 +4433,29 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9685</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.0031</v>
+        <v>0.082</v>
       </c>
       <c r="G126" t="n">
-        <v>1.7015</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="H126" t="n">
-        <v>2.8979</v>
+        <v>2.7723</v>
       </c>
     </row>
     <row r="127">
@@ -4465,29 +4465,29 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv','')</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','2'), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E127" t="n">
         <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>0.4153</v>
+        <v>0.4042</v>
       </c>
       <c r="G127" t="n">
-        <v>0.0345</v>
+        <v>0.0034</v>
       </c>
       <c r="H127" t="n">
-        <v>2.2125</v>
+        <v>2.2334</v>
       </c>
     </row>
     <row r="128">
@@ -4497,29 +4497,29 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('msc',''), list('detr','3'), list('sder',c(2,4,31))</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9809</v>
+        <v>0.9997</v>
       </c>
       <c r="F128" t="n">
-        <v>-0.0527</v>
+        <v>0.4525</v>
       </c>
       <c r="G128" t="n">
-        <v>1.6699</v>
+        <v>0.0849</v>
       </c>
       <c r="H128" t="n">
-        <v>2.9687</v>
+        <v>2.1411</v>
       </c>
     </row>
     <row r="129">
@@ -4529,11 +4529,11 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1))</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4542,16 +4542,16 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9802</v>
+        <v>0.9794</v>
       </c>
       <c r="F129" t="n">
-        <v>-0.0678</v>
+        <v>-0.0024</v>
       </c>
       <c r="G129" t="n">
-        <v>1.6772</v>
+        <v>1.6304</v>
       </c>
       <c r="H129" t="n">
-        <v>2.99</v>
+        <v>2.8969</v>
       </c>
     </row>
     <row r="130">
@@ -4561,29 +4561,29 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv','')</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9807</v>
+        <v>0.9685</v>
       </c>
       <c r="F130" t="n">
-        <v>-0.0523</v>
+        <v>-0.0031</v>
       </c>
       <c r="G130" t="n">
-        <v>1.6776</v>
+        <v>1.7015</v>
       </c>
       <c r="H130" t="n">
-        <v>2.9683</v>
+        <v>2.8979</v>
       </c>
     </row>
     <row r="131">
@@ -4593,29 +4593,29 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv','')</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9814000000000001</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>-0.0602</v>
+        <v>0.4153</v>
       </c>
       <c r="G131" t="n">
-        <v>1.671</v>
+        <v>0.0345</v>
       </c>
       <c r="H131" t="n">
-        <v>2.9794</v>
+        <v>2.2125</v>
       </c>
     </row>
     <row r="132">
@@ -4625,11 +4625,11 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4638,16 +4638,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9802</v>
+        <v>0.9809</v>
       </c>
       <c r="F132" t="n">
-        <v>-0.03</v>
+        <v>-0.0527</v>
       </c>
       <c r="G132" t="n">
-        <v>1.6744</v>
+        <v>1.6699</v>
       </c>
       <c r="H132" t="n">
-        <v>2.9367</v>
+        <v>2.9687</v>
       </c>
     </row>
     <row r="133">
@@ -4657,11 +4657,11 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9796</v>
+        <v>0.9802</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.0485</v>
+        <v>-0.0678</v>
       </c>
       <c r="G133" t="n">
-        <v>1.6773</v>
+        <v>1.6772</v>
       </c>
       <c r="H133" t="n">
-        <v>2.9629</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="134">
@@ -4689,11 +4689,11 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4702,16 +4702,16 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9789</v>
+        <v>0.9807</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.0345</v>
+        <v>-0.0523</v>
       </c>
       <c r="G134" t="n">
-        <v>1.6695</v>
+        <v>1.6776</v>
       </c>
       <c r="H134" t="n">
-        <v>2.943</v>
+        <v>2.9683</v>
       </c>
     </row>
     <row r="135">
@@ -4721,11 +4721,11 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4734,16 +4734,16 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9797</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.0525</v>
+        <v>-0.0602</v>
       </c>
       <c r="G135" t="n">
-        <v>1.6706</v>
+        <v>1.671</v>
       </c>
       <c r="H135" t="n">
-        <v>2.9685</v>
+        <v>2.9794</v>
       </c>
     </row>
     <row r="136">
@@ -4753,11 +4753,11 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0,3,31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4766,16 +4766,16 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.981</v>
+        <v>0.9802</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.0598</v>
+        <v>-0.03</v>
       </c>
       <c r="G136" t="n">
-        <v>1.6584</v>
+        <v>1.6744</v>
       </c>
       <c r="H136" t="n">
-        <v>2.9788</v>
+        <v>2.9367</v>
       </c>
     </row>
     <row r="137">
@@ -4785,29 +4785,29 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,2,11))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>0.9796</v>
       </c>
       <c r="F137" t="n">
-        <v>0.1471</v>
+        <v>-0.0485</v>
       </c>
       <c r="G137" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.6773</v>
       </c>
       <c r="H137" t="n">
-        <v>2.6723</v>
+        <v>2.9629</v>
       </c>
     </row>
     <row r="138">
@@ -4817,29 +4817,29 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9828</v>
+        <v>0.9789</v>
       </c>
       <c r="F138" t="n">
-        <v>0.1518</v>
+        <v>-0.0345</v>
       </c>
       <c r="G138" t="n">
-        <v>1.528</v>
+        <v>1.6695</v>
       </c>
       <c r="H138" t="n">
-        <v>2.6649</v>
+        <v>2.943</v>
       </c>
     </row>
     <row r="139">
@@ -4849,29 +4849,29 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>0.9797</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1129</v>
+        <v>-0.0525</v>
       </c>
       <c r="G139" t="n">
-        <v>0.0004</v>
+        <v>1.6706</v>
       </c>
       <c r="H139" t="n">
-        <v>2.7253</v>
+        <v>2.9685</v>
       </c>
     </row>
     <row r="140">
@@ -4881,29 +4881,29 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(0,3,31))</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9997</v>
+        <v>0.981</v>
       </c>
       <c r="F140" t="n">
-        <v>0.3742</v>
+        <v>-0.0598</v>
       </c>
       <c r="G140" t="n">
-        <v>0.0963</v>
+        <v>1.6584</v>
       </c>
       <c r="H140" t="n">
-        <v>2.289</v>
+        <v>2.9788</v>
       </c>
     </row>
     <row r="141">
@@ -4913,29 +4913,29 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,2,11))</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E141" t="n">
         <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>0.4467</v>
+        <v>0.1471</v>
       </c>
       <c r="G141" t="n">
-        <v>0.0231</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="H141" t="n">
-        <v>2.1523</v>
+        <v>2.6723</v>
       </c>
     </row>
     <row r="142">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -4977,29 +4977,29 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,21))</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 10, 'learning_rate': 0.05, 'colsample_bytree': 1.0}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E143" t="n">
         <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1036</v>
+        <v>0.1129</v>
       </c>
       <c r="G143" t="n">
-        <v>0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H143" t="n">
-        <v>2.7396</v>
+        <v>2.7253</v>
       </c>
     </row>
     <row r="144">
@@ -5009,29 +5009,29 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9947</v>
+        <v>0.9997</v>
       </c>
       <c r="F144" t="n">
-        <v>0.1123</v>
+        <v>0.3742</v>
       </c>
       <c r="G144" t="n">
-        <v>0.6302</v>
+        <v>0.0963</v>
       </c>
       <c r="H144" t="n">
-        <v>2.7263</v>
+        <v>2.289</v>
       </c>
     </row>
     <row r="145">
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -5073,29 +5073,29 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0.9828</v>
       </c>
       <c r="F146" t="n">
-        <v>0.415</v>
+        <v>0.1518</v>
       </c>
       <c r="G146" t="n">
-        <v>0.0009</v>
+        <v>1.528</v>
       </c>
       <c r="H146" t="n">
-        <v>2.2132</v>
+        <v>2.6649</v>
       </c>
     </row>
     <row r="147">
@@ -5105,29 +5105,29 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,25))</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 10, 'learning_rate': 0.05, 'colsample_bytree': 1.0}</t>
         </is>
       </c>
       <c r="E147" t="n">
         <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>0.4114</v>
+        <v>0.1036</v>
       </c>
       <c r="G147" t="n">
-        <v>0.0004</v>
+        <v>0.012</v>
       </c>
       <c r="H147" t="n">
-        <v>2.2199</v>
+        <v>2.7396</v>
       </c>
     </row>
     <row r="148">
@@ -5137,29 +5137,29 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(1,3,31))</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.9978</v>
+        <v>0.9947</v>
       </c>
       <c r="F148" t="n">
-        <v>0.4108</v>
+        <v>0.1123</v>
       </c>
       <c r="G148" t="n">
-        <v>0.2826</v>
+        <v>0.6302</v>
       </c>
       <c r="H148" t="n">
-        <v>2.2211</v>
+        <v>2.7263</v>
       </c>
     </row>
     <row r="149">
@@ -5169,29 +5169,29 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('sder',c(2,3,21))</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E149" t="n">
         <v>1</v>
       </c>
       <c r="F149" t="n">
-        <v>0.4021</v>
+        <v>0.4467</v>
       </c>
       <c r="G149" t="n">
-        <v>0.0004</v>
+        <v>0.0231</v>
       </c>
       <c r="H149" t="n">
-        <v>2.2373</v>
+        <v>2.1523</v>
       </c>
     </row>
     <row r="150">
@@ -5201,29 +5201,29 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 21))</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E150" t="n">
         <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4136</v>
+        <v>0.415</v>
       </c>
       <c r="G150" t="n">
-        <v>0.0353</v>
+        <v>0.0009</v>
       </c>
       <c r="H150" t="n">
-        <v>2.2157</v>
+        <v>2.2132</v>
       </c>
     </row>
     <row r="151">
@@ -5233,29 +5233,29 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 25))</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 300, 'max_depth': 10, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E151" t="n">
         <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>0.4094</v>
+        <v>0.4114</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0353</v>
+        <v>0.0004</v>
       </c>
       <c r="H151" t="n">
-        <v>2.2236</v>
+        <v>2.2199</v>
       </c>
     </row>
     <row r="152">
@@ -5265,29 +5265,29 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 27))</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.9978</v>
       </c>
       <c r="F152" t="n">
-        <v>0.4093</v>
+        <v>0.4108</v>
       </c>
       <c r="G152" t="n">
-        <v>0.0005</v>
+        <v>0.2826</v>
       </c>
       <c r="H152" t="n">
-        <v>2.2239</v>
+        <v>2.2211</v>
       </c>
     </row>
     <row r="153">
@@ -5297,11 +5297,11 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 2, 31))</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5313,13 +5313,13 @@
         <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>0.4094</v>
+        <v>0.4021</v>
       </c>
       <c r="G153" t="n">
         <v>0.0004</v>
       </c>
       <c r="H153" t="n">
-        <v>2.2237</v>
+        <v>2.2373</v>
       </c>
     </row>
     <row r="154">
@@ -5329,29 +5329,29 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 15))</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E154" t="n">
         <v>1</v>
       </c>
       <c r="F154" t="n">
-        <v>0.4</v>
+        <v>0.4136</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0004</v>
+        <v>0.0353</v>
       </c>
       <c r="H154" t="n">
-        <v>2.2414</v>
+        <v>2.2157</v>
       </c>
     </row>
     <row r="155">
@@ -5361,29 +5361,29 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 17))</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E155" t="n">
         <v>1</v>
       </c>
       <c r="F155" t="n">
-        <v>0.6074000000000001</v>
+        <v>0.4094</v>
       </c>
       <c r="G155" t="n">
-        <v>0.0003</v>
+        <v>0.0353</v>
       </c>
       <c r="H155" t="n">
-        <v>1.8131</v>
+        <v>2.2236</v>
       </c>
     </row>
     <row r="156">
@@ -5393,29 +5393,29 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 19))</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.9993</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>0.6347</v>
+        <v>0.4093</v>
       </c>
       <c r="G156" t="n">
-        <v>0.1232</v>
+        <v>0.0005</v>
       </c>
       <c r="H156" t="n">
-        <v>1.749</v>
+        <v>2.2239</v>
       </c>
     </row>
     <row r="157">
@@ -5425,29 +5425,29 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 1.0}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E157" t="n">
         <v>1</v>
       </c>
       <c r="F157" t="n">
-        <v>0.66</v>
+        <v>0.4094</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0126</v>
+        <v>0.0004</v>
       </c>
       <c r="H157" t="n">
-        <v>1.6873</v>
+        <v>2.2237</v>
       </c>
     </row>
     <row r="158">
@@ -5457,29 +5457,29 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(0,3,31))</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
-        <v>0.7134</v>
+        <v>0.4</v>
       </c>
       <c r="G158" t="n">
-        <v>0.09</v>
+        <v>0.0004</v>
       </c>
       <c r="H158" t="n">
-        <v>1.549</v>
+        <v>2.2414</v>
       </c>
     </row>
     <row r="159">
@@ -5489,29 +5489,29 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.968</v>
+        <v>1</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0698</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="G159" t="n">
-        <v>1.6224</v>
+        <v>0.0003</v>
       </c>
       <c r="H159" t="n">
-        <v>2.7907</v>
+        <v>1.8131</v>
       </c>
     </row>
     <row r="160">
@@ -5521,29 +5521,29 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,25))</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0.9993</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3032</v>
+        <v>0.6347</v>
       </c>
       <c r="G160" t="n">
-        <v>0.0039</v>
+        <v>0.1232</v>
       </c>
       <c r="H160" t="n">
-        <v>2.4153</v>
+        <v>1.749</v>
       </c>
     </row>
     <row r="161">
@@ -5553,29 +5553,29 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(1,3,31))</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 1.0}</t>
         </is>
       </c>
       <c r="E161" t="n">
         <v>1</v>
       </c>
       <c r="F161" t="n">
-        <v>0.2926</v>
+        <v>0.66</v>
       </c>
       <c r="G161" t="n">
-        <v>0.0005</v>
+        <v>0.0126</v>
       </c>
       <c r="H161" t="n">
-        <v>2.4337</v>
+        <v>1.6873</v>
       </c>
     </row>
     <row r="162">
@@ -5585,29 +5585,29 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('sder',c(2,3,21))</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9611</v>
+        <v>0.9996</v>
       </c>
       <c r="F162" t="n">
-        <v>0.1215</v>
+        <v>0.7134</v>
       </c>
       <c r="G162" t="n">
-        <v>1.6355</v>
+        <v>0.09</v>
       </c>
       <c r="H162" t="n">
-        <v>2.712</v>
+        <v>1.549</v>
       </c>
     </row>
     <row r="163">
@@ -5617,29 +5617,29 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9947</v>
+        <v>0.968</v>
       </c>
       <c r="F163" t="n">
-        <v>0.202</v>
+        <v>0.0698</v>
       </c>
       <c r="G163" t="n">
-        <v>0.467</v>
+        <v>1.6224</v>
       </c>
       <c r="H163" t="n">
-        <v>2.5848</v>
+        <v>2.7907</v>
       </c>
     </row>
     <row r="164">
@@ -5649,29 +5649,29 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2')</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 200, 'max_depth': 5, 'learning_rate': 0.1, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E164" t="n">
         <v>1</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3827</v>
+        <v>0.3032</v>
       </c>
       <c r="G164" t="n">
-        <v>0.0032</v>
+        <v>0.0039</v>
       </c>
       <c r="H164" t="n">
-        <v>2.2734</v>
+        <v>2.4153</v>
       </c>
     </row>
     <row r="165">
@@ -5681,29 +5681,29 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc','')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.1, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9794</v>
+        <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>-0.0024</v>
+        <v>0.2926</v>
       </c>
       <c r="G165" t="n">
-        <v>1.6304</v>
+        <v>0.0005</v>
       </c>
       <c r="H165" t="n">
-        <v>2.8969</v>
+        <v>2.4337</v>
       </c>
     </row>
     <row r="166">
@@ -5713,29 +5713,29 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('msc','')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(0, 3, 21))</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
+          <t>{'subsample': 0.9, 'n_estimators': 100, 'max_depth': 5, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8853</v>
+        <v>0.9611</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0509</v>
+        <v>0.1215</v>
       </c>
       <c r="G166" t="n">
-        <v>1.7506</v>
+        <v>1.6355</v>
       </c>
       <c r="H166" t="n">
-        <v>2.819</v>
+        <v>2.712</v>
       </c>
     </row>
     <row r="167">
@@ -5745,29 +5745,29 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>0.9947</v>
       </c>
       <c r="F167" t="n">
-        <v>0.2567</v>
+        <v>0.202</v>
       </c>
       <c r="G167" t="n">
-        <v>0.0004</v>
+        <v>0.467</v>
       </c>
       <c r="H167" t="n">
-        <v>2.4947</v>
+        <v>2.5848</v>
       </c>
     </row>
     <row r="168">
@@ -5777,29 +5777,29 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2,3,15))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('snv',''), list('detr','2'), list('sder',c(2,3,15))</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="F168" t="n">
-        <v>0.4526</v>
+        <v>0.3827</v>
       </c>
       <c r="G168" t="n">
-        <v>0.0955</v>
+        <v>0.0032</v>
       </c>
       <c r="H168" t="n">
-        <v>2.1407</v>
+        <v>2.2734</v>
       </c>
     </row>
     <row r="169">
@@ -5809,29 +5809,29 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 100, 'max_depth': 7, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1</v>
+        <v>0.9794</v>
       </c>
       <c r="F169" t="n">
-        <v>0.5800999999999999</v>
+        <v>-0.0024</v>
       </c>
       <c r="G169" t="n">
-        <v>0.0003</v>
+        <v>1.6304</v>
       </c>
       <c r="H169" t="n">
-        <v>1.8751</v>
+        <v>2.8969</v>
       </c>
     </row>
     <row r="170">
@@ -5841,29 +5841,29 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(950,750,1)), list('msc','')</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 0.8, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.01, 'colsample_bytree': 0.5}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1</v>
+        <v>0.8853</v>
       </c>
       <c r="F170" t="n">
-        <v>0.2911</v>
+        <v>0.0509</v>
       </c>
       <c r="G170" t="n">
-        <v>0.0042</v>
+        <v>1.7506</v>
       </c>
       <c r="H170" t="n">
-        <v>2.4362</v>
+        <v>2.819</v>
       </c>
     </row>
     <row r="171">
@@ -5873,29 +5873,29 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(1,3,15))</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+          <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="F171" t="n">
-        <v>0.4121</v>
+        <v>0.2567</v>
       </c>
       <c r="G171" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0004</v>
       </c>
       <c r="H171" t="n">
-        <v>2.2185</v>
+        <v>2.4947</v>
       </c>
     </row>
     <row r="172">
@@ -5905,28 +5905,156 @@
         </is>
       </c>
       <c r="B172" t="n">
+        <v>171</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('msc',''), list('sder',c(2,3,15))</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0.9996</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="H172" t="n">
+        <v>2.1407</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>C18.1n9</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>172</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>list('snv',''),list('sder',c(1,3,9)),list('red',c(10,10,1))</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>{'subsample': 0.8, 'n_estimators': 500, 'max_depth': 7, 'learning_rate': 0.05, 'colsample_bytree': 0.8}</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>0.5800999999999999</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="H173" t="n">
+        <v>1.8751</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>C18.1n9</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>173</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('sder',c(2,4,21)), list('snv','')</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>{'subsample': 0.7, 'n_estimators': 500, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="H174" t="n">
+        <v>2.4362</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>C18.1n9</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>174</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>list('adj',''), list('red',c(1,1300,1)), list('snv',''), list('detr','3'), list('sder',c(2,4,25))</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>{'subsample': 0.9, 'n_estimators': 200, 'max_depth': 3, 'learning_rate': 0.05, 'colsample_bytree': 0.3}</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="H175" t="n">
+        <v>2.2185</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>C18.1n9</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
         <v>175</v>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C176" t="inlineStr">
         <is>
           <t>list('adj',''), list('ref2abs',''), list('red',c(1,1300,1)), list('sder',c(1,3,31)), list('snv','')</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D176" t="inlineStr">
         <is>
           <t>{'subsample': 1.0, 'n_estimators': 300, 'max_depth': 3, 'learning_rate': 0.2, 'colsample_bytree': 0.8}</t>
         </is>
       </c>
-      <c r="E172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" t="n">
+      <c r="E176" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" t="n">
         <v>0.222</v>
       </c>
-      <c r="G172" t="n">
+      <c r="G176" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="H172" t="n">
+      <c r="H176" t="n">
         <v>2.5522</v>
       </c>
     </row>
